--- a/estadistica2/data/cabal.xlsx
+++ b/estadistica2/data/cabal.xlsx
@@ -1,36 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BD32948-76B0-964B-BBA1-A8C42EDC1BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86A1C5A2-3D57-454E-8669-DCBD446B794C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1880" yWindow="500" windowWidth="24800" windowHeight="13580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Democracia" sheetId="1" r:id="rId1"/>
     <sheet name="Descripción_Variables" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos_Democracia!$A$1:$G$1</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="36">
-  <si>
-    <t>País</t>
-  </si>
-  <si>
-    <t>Año</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="42">
   <si>
     <t>Índice_de_Democracia</t>
   </si>
@@ -113,10 +104,19 @@
     <t>Índice que mide el nivel de democracia (0 = autoritario, 10 = democracia plena)</t>
   </si>
   <si>
+    <t>Índice (0-10)</t>
+  </si>
+  <si>
     <t>Porcentaje de crecimiento anual del Producto Interno Bruto (PIB)</t>
   </si>
   <si>
+    <t>Porcentaje</t>
+  </si>
+  <si>
     <t>Índice Gini que mide la desigualdad (0 = igualdad perfecta, 100 = desigualdad total)</t>
+  </si>
+  <si>
+    <t>Índice (0-100)</t>
   </si>
   <si>
     <t>Porcentaje de la población con acceso a agua potable</t>
@@ -125,20 +125,35 @@
     <t>Porcentaje de mujeres en la fuerza laboral del país</t>
   </si>
   <si>
-    <t>Índice (0-10)</t>
+    <t>pais</t>
   </si>
   <si>
-    <t>Porcentaje</t>
+    <t>año</t>
   </si>
   <si>
-    <t>Índice (0-100)</t>
+    <t>indice_democracia</t>
+  </si>
+  <si>
+    <t>crecimiento</t>
+  </si>
+  <si>
+    <t>indice_gini</t>
+  </si>
+  <si>
+    <t>agua_potable</t>
+  </si>
+  <si>
+    <t>mujeres_fuerza_laboral</t>
+  </si>
+  <si>
+    <t>liberalizacion_economica</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +169,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -163,7 +184,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -186,13 +207,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -213,9 +252,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -253,7 +292,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -287,7 +326,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -322,10 +360,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -499,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G559"/>
+  <dimension ref="A1:H559"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -509,34 +546,38 @@
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
       </c>
       <c r="B2">
         <v>1990</v>
@@ -556,10 +597,13 @@
       <c r="G2">
         <v>52.61</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>1991</v>
@@ -579,10 +623,13 @@
       <c r="G3">
         <v>54.83</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>1992</v>
@@ -602,10 +649,13 @@
       <c r="G4">
         <v>51.68</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1993</v>
@@ -625,10 +675,13 @@
       <c r="G5">
         <v>41.03</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>1994</v>
@@ -648,10 +701,13 @@
       <c r="G6">
         <v>59.11</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>1995</v>
@@ -671,10 +727,13 @@
       <c r="G7">
         <v>48.25</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>1996</v>
@@ -694,10 +753,13 @@
       <c r="G8">
         <v>49.2</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>1997</v>
@@ -717,10 +779,13 @@
       <c r="G9">
         <v>38.76</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>1998</v>
@@ -740,10 +805,13 @@
       <c r="G10">
         <v>42.33</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11">
         <v>1999</v>
@@ -763,10 +831,13 @@
       <c r="G11">
         <v>45.38</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B12">
         <v>2000</v>
@@ -786,10 +857,13 @@
       <c r="G12">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B13">
         <v>2001</v>
@@ -809,10 +883,13 @@
       <c r="G13">
         <v>49.14</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14">
         <v>2002</v>
@@ -832,10 +909,13 @@
       <c r="G14">
         <v>51.06</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B15">
         <v>2003</v>
@@ -855,10 +935,13 @@
       <c r="G15">
         <v>44.87</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B16">
         <v>2004</v>
@@ -878,10 +961,13 @@
       <c r="G16">
         <v>40.58</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B17">
         <v>2005</v>
@@ -901,10 +987,13 @@
       <c r="G17">
         <v>44.45</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B18">
         <v>2006</v>
@@ -924,10 +1013,13 @@
       <c r="G18">
         <v>57.68</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B19">
         <v>2007</v>
@@ -947,10 +1039,13 @@
       <c r="G19">
         <v>45.73</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20">
         <v>2008</v>
@@ -970,10 +1065,13 @@
       <c r="G20">
         <v>49.16</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B21">
         <v>2009</v>
@@ -993,10 +1091,13 @@
       <c r="G21">
         <v>31.33</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B22">
         <v>2010</v>
@@ -1016,10 +1117,13 @@
       <c r="G22">
         <v>36.81</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B23">
         <v>2011</v>
@@ -1039,10 +1143,13 @@
       <c r="G23">
         <v>37.51</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B24">
         <v>2012</v>
@@ -1062,10 +1169,13 @@
       <c r="G24">
         <v>30.59</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B25">
         <v>2013</v>
@@ -1085,10 +1195,13 @@
       <c r="G25">
         <v>53.89</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B26">
         <v>2014</v>
@@ -1108,10 +1221,13 @@
       <c r="G26">
         <v>40.840000000000003</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B27">
         <v>2015</v>
@@ -1131,10 +1247,13 @@
       <c r="G27">
         <v>39.15</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B28">
         <v>2016</v>
@@ -1154,10 +1273,13 @@
       <c r="G28">
         <v>43.97</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B29">
         <v>2017</v>
@@ -1177,10 +1299,13 @@
       <c r="G29">
         <v>36.979999999999997</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B30">
         <v>2018</v>
@@ -1200,10 +1325,13 @@
       <c r="G30">
         <v>47.9</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B31">
         <v>2019</v>
@@ -1223,10 +1351,13 @@
       <c r="G31">
         <v>58.37</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B32">
         <v>2020</v>
@@ -1246,10 +1377,13 @@
       <c r="G32">
         <v>39.58</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B33">
         <v>1990</v>
@@ -1269,10 +1403,13 @@
       <c r="G33">
         <v>47.36</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B34">
         <v>1991</v>
@@ -1292,10 +1429,13 @@
       <c r="G34">
         <v>57.18</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B35">
         <v>1992</v>
@@ -1315,10 +1455,13 @@
       <c r="G35">
         <v>39.369999999999997</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B36">
         <v>1993</v>
@@ -1338,10 +1481,13 @@
       <c r="G36">
         <v>46.43</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B37">
         <v>1994</v>
@@ -1361,10 +1507,13 @@
       <c r="G37">
         <v>54.56</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B38">
         <v>1995</v>
@@ -1384,10 +1533,13 @@
       <c r="G38">
         <v>32</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B39">
         <v>1996</v>
@@ -1407,10 +1559,13 @@
       <c r="G39">
         <v>57.66</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B40">
         <v>1997</v>
@@ -1430,10 +1585,13 @@
       <c r="G40">
         <v>51.91</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B41">
         <v>1998</v>
@@ -1453,10 +1611,13 @@
       <c r="G41">
         <v>46.04</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B42">
         <v>1999</v>
@@ -1476,10 +1637,13 @@
       <c r="G42">
         <v>42.41</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B43">
         <v>2000</v>
@@ -1499,10 +1663,13 @@
       <c r="G43">
         <v>48.76</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B44">
         <v>2001</v>
@@ -1522,10 +1689,13 @@
       <c r="G44">
         <v>52.97</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B45">
         <v>2002</v>
@@ -1545,10 +1715,13 @@
       <c r="G45">
         <v>34.049999999999997</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B46">
         <v>2003</v>
@@ -1568,10 +1741,13 @@
       <c r="G46">
         <v>40.96</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B47">
         <v>2004</v>
@@ -1591,10 +1767,13 @@
       <c r="G47">
         <v>55.11</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B48">
         <v>2005</v>
@@ -1614,10 +1793,13 @@
       <c r="G48">
         <v>55.57</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B49">
         <v>2006</v>
@@ -1637,10 +1819,13 @@
       <c r="G49">
         <v>31.79</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B50">
         <v>2007</v>
@@ -1660,10 +1845,13 @@
       <c r="G50">
         <v>38.49</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B51">
         <v>2008</v>
@@ -1683,10 +1871,13 @@
       <c r="G51">
         <v>56.38</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B52">
         <v>2009</v>
@@ -1706,10 +1897,13 @@
       <c r="G52">
         <v>53.21</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B53">
         <v>2010</v>
@@ -1729,10 +1923,13 @@
       <c r="G53">
         <v>54.18</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B54">
         <v>2011</v>
@@ -1752,10 +1949,13 @@
       <c r="G54">
         <v>33.67</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B55">
         <v>2012</v>
@@ -1775,10 +1975,13 @@
       <c r="G55">
         <v>51.04</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B56">
         <v>2013</v>
@@ -1798,10 +2001,13 @@
       <c r="G56">
         <v>32.93</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B57">
         <v>2014</v>
@@ -1821,10 +2027,13 @@
       <c r="G57">
         <v>39.380000000000003</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B58">
         <v>2015</v>
@@ -1844,10 +2053,13 @@
       <c r="G58">
         <v>59.39</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B59">
         <v>2016</v>
@@ -1867,10 +2079,13 @@
       <c r="G59">
         <v>35.64</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B60">
         <v>2017</v>
@@ -1890,10 +2105,13 @@
       <c r="G60">
         <v>35.35</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B61">
         <v>2018</v>
@@ -1913,10 +2131,13 @@
       <c r="G61">
         <v>50.37</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B62">
         <v>2019</v>
@@ -1936,10 +2157,13 @@
       <c r="G62">
         <v>50.63</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B63">
         <v>2020</v>
@@ -1959,10 +2183,13 @@
       <c r="G63">
         <v>54.79</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B64">
         <v>1990</v>
@@ -1982,10 +2209,13 @@
       <c r="G64">
         <v>30.64</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B65">
         <v>1991</v>
@@ -2005,10 +2235,13 @@
       <c r="G65">
         <v>53.51</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B66">
         <v>1992</v>
@@ -2028,10 +2261,13 @@
       <c r="G66">
         <v>35.979999999999997</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B67">
         <v>1993</v>
@@ -2051,10 +2287,13 @@
       <c r="G67">
         <v>46.72</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B68">
         <v>1994</v>
@@ -2074,10 +2313,13 @@
       <c r="G68">
         <v>54.97</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B69">
         <v>1995</v>
@@ -2097,10 +2339,13 @@
       <c r="G69">
         <v>38.81</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B70">
         <v>1996</v>
@@ -2120,10 +2365,13 @@
       <c r="G70">
         <v>54.58</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B71">
         <v>1997</v>
@@ -2143,10 +2391,13 @@
       <c r="G71">
         <v>42.83</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B72">
         <v>1998</v>
@@ -2166,10 +2417,13 @@
       <c r="G72">
         <v>55.02</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B73">
         <v>1999</v>
@@ -2189,10 +2443,13 @@
       <c r="G73">
         <v>50.65</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B74">
         <v>2000</v>
@@ -2212,10 +2469,13 @@
       <c r="G74">
         <v>37.15</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B75">
         <v>2001</v>
@@ -2235,10 +2495,13 @@
       <c r="G75">
         <v>59.55</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B76">
         <v>2002</v>
@@ -2258,10 +2521,13 @@
       <c r="G76">
         <v>33</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B77">
         <v>2003</v>
@@ -2281,10 +2547,13 @@
       <c r="G77">
         <v>54.46</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B78">
         <v>2004</v>
@@ -2304,10 +2573,13 @@
       <c r="G78">
         <v>36</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B79">
         <v>2005</v>
@@ -2327,10 +2599,13 @@
       <c r="G79">
         <v>32.61</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B80">
         <v>2006</v>
@@ -2350,10 +2625,13 @@
       <c r="G80">
         <v>34.46</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B81">
         <v>2007</v>
@@ -2373,10 +2651,13 @@
       <c r="G81">
         <v>40.619999999999997</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -2396,10 +2677,13 @@
       <c r="G82">
         <v>52.26</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B83">
         <v>2009</v>
@@ -2419,10 +2703,13 @@
       <c r="G83">
         <v>42.21</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B84">
         <v>2010</v>
@@ -2442,10 +2729,13 @@
       <c r="G84">
         <v>46.28</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B85">
         <v>2011</v>
@@ -2465,10 +2755,13 @@
       <c r="G85">
         <v>49.13</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B86">
         <v>2012</v>
@@ -2488,10 +2781,13 @@
       <c r="G86">
         <v>53.05</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B87">
         <v>2013</v>
@@ -2511,10 +2807,13 @@
       <c r="G87">
         <v>31.77</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B88">
         <v>2014</v>
@@ -2534,10 +2833,13 @@
       <c r="G88">
         <v>48.51</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B89">
         <v>2015</v>
@@ -2557,10 +2859,13 @@
       <c r="G89">
         <v>51.28</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B90">
         <v>2016</v>
@@ -2580,10 +2885,13 @@
       <c r="G90">
         <v>52.07</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B91">
         <v>2017</v>
@@ -2603,10 +2911,13 @@
       <c r="G91">
         <v>47.02</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B92">
         <v>2018</v>
@@ -2626,10 +2937,13 @@
       <c r="G92">
         <v>31.4</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B93">
         <v>2019</v>
@@ -2649,10 +2963,13 @@
       <c r="G93">
         <v>41.36</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B94">
         <v>2020</v>
@@ -2672,10 +2989,13 @@
       <c r="G94">
         <v>42.09</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B95">
         <v>1990</v>
@@ -2695,10 +3015,13 @@
       <c r="G95">
         <v>36.49</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B96">
         <v>1991</v>
@@ -2718,10 +3041,13 @@
       <c r="G96">
         <v>45.56</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B97">
         <v>1992</v>
@@ -2741,10 +3067,13 @@
       <c r="G97">
         <v>33.119999999999997</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B98">
         <v>1993</v>
@@ -2764,10 +3093,13 @@
       <c r="G98">
         <v>33.619999999999997</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B99">
         <v>1994</v>
@@ -2787,10 +3119,13 @@
       <c r="G99">
         <v>39.68</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B100">
         <v>1995</v>
@@ -2810,10 +3145,13 @@
       <c r="G100">
         <v>44.04</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B101">
         <v>1996</v>
@@ -2833,10 +3171,13 @@
       <c r="G101">
         <v>34.5</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B102">
         <v>1997</v>
@@ -2856,10 +3197,13 @@
       <c r="G102">
         <v>56.2</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B103">
         <v>1998</v>
@@ -2879,10 +3223,13 @@
       <c r="G103">
         <v>46.15</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B104">
         <v>1999</v>
@@ -2902,10 +3249,13 @@
       <c r="G104">
         <v>58.09</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B105">
         <v>2000</v>
@@ -2925,10 +3275,13 @@
       <c r="G105">
         <v>35.89</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B106">
         <v>2001</v>
@@ -2948,10 +3301,13 @@
       <c r="G106">
         <v>57.15</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B107">
         <v>2002</v>
@@ -2971,10 +3327,13 @@
       <c r="G107">
         <v>52.87</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B108">
         <v>2003</v>
@@ -2994,10 +3353,13 @@
       <c r="G108">
         <v>39.79</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B109">
         <v>2004</v>
@@ -3017,10 +3379,13 @@
       <c r="G109">
         <v>40.119999999999997</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B110">
         <v>2005</v>
@@ -3040,10 +3405,13 @@
       <c r="G110">
         <v>54.35</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B111">
         <v>2006</v>
@@ -3063,10 +3431,13 @@
       <c r="G111">
         <v>42.7</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B112">
         <v>2007</v>
@@ -3086,10 +3457,13 @@
       <c r="G112">
         <v>30.13</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B113">
         <v>2008</v>
@@ -3109,10 +3483,13 @@
       <c r="G113">
         <v>39.4</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B114">
         <v>2009</v>
@@ -3132,10 +3509,13 @@
       <c r="G114">
         <v>43.31</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B115">
         <v>2010</v>
@@ -3155,10 +3535,13 @@
       <c r="G115">
         <v>55.54</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B116">
         <v>2011</v>
@@ -3178,10 +3561,13 @@
       <c r="G116">
         <v>57.58</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B117">
         <v>2012</v>
@@ -3201,10 +3587,13 @@
       <c r="G117">
         <v>39.83</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B118">
         <v>2013</v>
@@ -3224,10 +3613,13 @@
       <c r="G118">
         <v>32.56</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B119">
         <v>2014</v>
@@ -3247,10 +3639,13 @@
       <c r="G119">
         <v>44.45</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B120">
         <v>2015</v>
@@ -3270,10 +3665,13 @@
       <c r="G120">
         <v>55.06</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B121">
         <v>2016</v>
@@ -3293,10 +3691,13 @@
       <c r="G121">
         <v>52.46</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B122">
         <v>2017</v>
@@ -3316,10 +3717,13 @@
       <c r="G122">
         <v>36.299999999999997</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B123">
         <v>2018</v>
@@ -3339,10 +3743,13 @@
       <c r="G123">
         <v>31.38</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B124">
         <v>2019</v>
@@ -3362,10 +3769,13 @@
       <c r="G124">
         <v>52.71</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B125">
         <v>2020</v>
@@ -3385,10 +3795,13 @@
       <c r="G125">
         <v>43.16</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B126">
         <v>1990</v>
@@ -3408,10 +3821,13 @@
       <c r="G126">
         <v>57.58</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B127">
         <v>1991</v>
@@ -3431,10 +3847,13 @@
       <c r="G127">
         <v>34.93</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B128">
         <v>1992</v>
@@ -3454,10 +3873,13 @@
       <c r="G128">
         <v>41.12</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B129">
         <v>1993</v>
@@ -3477,10 +3899,13 @@
       <c r="G129">
         <v>50.84</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B130">
         <v>1994</v>
@@ -3500,10 +3925,13 @@
       <c r="G130">
         <v>33.24</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B131">
         <v>1995</v>
@@ -3523,10 +3951,13 @@
       <c r="G131">
         <v>48.71</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B132">
         <v>1996</v>
@@ -3546,10 +3977,13 @@
       <c r="G132">
         <v>42.12</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B133">
         <v>1997</v>
@@ -3569,10 +4003,13 @@
       <c r="G133">
         <v>36.47</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B134">
         <v>1998</v>
@@ -3592,10 +4029,13 @@
       <c r="G134">
         <v>30.19</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B135">
         <v>1999</v>
@@ -3615,10 +4055,13 @@
       <c r="G135">
         <v>55.65</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B136">
         <v>2000</v>
@@ -3638,10 +4081,13 @@
       <c r="G136">
         <v>55.93</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B137">
         <v>2001</v>
@@ -3661,10 +4107,13 @@
       <c r="G137">
         <v>53.27</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B138">
         <v>2002</v>
@@ -3684,10 +4133,13 @@
       <c r="G138">
         <v>54.29</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B139">
         <v>2003</v>
@@ -3707,10 +4159,13 @@
       <c r="G139">
         <v>55.88</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B140">
         <v>2004</v>
@@ -3730,10 +4185,13 @@
       <c r="G140">
         <v>35.96</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B141">
         <v>2005</v>
@@ -3753,10 +4211,13 @@
       <c r="G141">
         <v>53.3</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B142">
         <v>2006</v>
@@ -3776,10 +4237,13 @@
       <c r="G142">
         <v>45.04</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B143">
         <v>2007</v>
@@ -3799,10 +4263,13 @@
       <c r="G143">
         <v>53.94</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B144">
         <v>2008</v>
@@ -3822,10 +4289,13 @@
       <c r="G144">
         <v>49.82</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B145">
         <v>2009</v>
@@ -3845,10 +4315,13 @@
       <c r="G145">
         <v>56.02</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B146">
         <v>2010</v>
@@ -3868,10 +4341,13 @@
       <c r="G146">
         <v>35.31</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B147">
         <v>2011</v>
@@ -3891,10 +4367,13 @@
       <c r="G147">
         <v>54.01</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B148">
         <v>2012</v>
@@ -3914,10 +4393,13 @@
       <c r="G148">
         <v>34.47</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B149">
         <v>2013</v>
@@ -3937,10 +4419,13 @@
       <c r="G149">
         <v>39.1</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B150">
         <v>2014</v>
@@ -3960,10 +4445,13 @@
       <c r="G150">
         <v>30.03</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B151">
         <v>2015</v>
@@ -3983,10 +4471,13 @@
       <c r="G151">
         <v>48.79</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B152">
         <v>2016</v>
@@ -4006,10 +4497,13 @@
       <c r="G152">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B153">
         <v>2017</v>
@@ -4029,10 +4523,13 @@
       <c r="G153">
         <v>41.85</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B154">
         <v>2018</v>
@@ -4052,10 +4549,13 @@
       <c r="G154">
         <v>36.74</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B155">
         <v>2019</v>
@@ -4075,10 +4575,13 @@
       <c r="G155">
         <v>38.68</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B156">
         <v>2020</v>
@@ -4098,10 +4601,13 @@
       <c r="G156">
         <v>53.91</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B157">
         <v>1990</v>
@@ -4121,10 +4627,13 @@
       <c r="G157">
         <v>35.75</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B158">
         <v>1991</v>
@@ -4144,10 +4653,13 @@
       <c r="G158">
         <v>31.58</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B159">
         <v>1992</v>
@@ -4167,10 +4679,13 @@
       <c r="G159">
         <v>42.8</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B160">
         <v>1993</v>
@@ -4190,10 +4705,13 @@
       <c r="G160">
         <v>42.4</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B161">
         <v>1994</v>
@@ -4213,10 +4731,13 @@
       <c r="G161">
         <v>33.56</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B162">
         <v>1995</v>
@@ -4236,10 +4757,13 @@
       <c r="G162">
         <v>42.93</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B163">
         <v>1996</v>
@@ -4259,10 +4783,13 @@
       <c r="G163">
         <v>37.520000000000003</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B164">
         <v>1997</v>
@@ -4282,10 +4809,13 @@
       <c r="G164">
         <v>40.89</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B165">
         <v>1998</v>
@@ -4305,10 +4835,13 @@
       <c r="G165">
         <v>45.85</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B166">
         <v>1999</v>
@@ -4328,10 +4861,13 @@
       <c r="G166">
         <v>33.57</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B167">
         <v>2000</v>
@@ -4351,10 +4887,13 @@
       <c r="G167">
         <v>36.090000000000003</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B168">
         <v>2001</v>
@@ -4374,10 +4913,13 @@
       <c r="G168">
         <v>46.77</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B169">
         <v>2002</v>
@@ -4397,10 +4939,13 @@
       <c r="G169">
         <v>47.54</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B170">
         <v>2003</v>
@@ -4420,10 +4965,13 @@
       <c r="G170">
         <v>46.46</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B171">
         <v>2004</v>
@@ -4443,10 +4991,13 @@
       <c r="G171">
         <v>48.71</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B172">
         <v>2005</v>
@@ -4466,10 +5017,13 @@
       <c r="G172">
         <v>33.18</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B173">
         <v>2006</v>
@@ -4489,10 +5043,13 @@
       <c r="G173">
         <v>45.47</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B174">
         <v>2007</v>
@@ -4512,10 +5069,13 @@
       <c r="G174">
         <v>51.28</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B175">
         <v>2008</v>
@@ -4535,10 +5095,13 @@
       <c r="G175">
         <v>30.06</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B176">
         <v>2009</v>
@@ -4558,10 +5121,13 @@
       <c r="G176">
         <v>43.2</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B177">
         <v>2010</v>
@@ -4581,10 +5147,13 @@
       <c r="G177">
         <v>38.71</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B178">
         <v>2011</v>
@@ -4604,10 +5173,13 @@
       <c r="G178">
         <v>33.93</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B179">
         <v>2012</v>
@@ -4627,10 +5199,13 @@
       <c r="G179">
         <v>45.99</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B180">
         <v>2013</v>
@@ -4650,10 +5225,13 @@
       <c r="G180">
         <v>51.97</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B181">
         <v>2014</v>
@@ -4673,10 +5251,13 @@
       <c r="G181">
         <v>38.81</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B182">
         <v>2015</v>
@@ -4696,10 +5277,13 @@
       <c r="G182">
         <v>42.79</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B183">
         <v>2016</v>
@@ -4719,10 +5303,13 @@
       <c r="G183">
         <v>48.2</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B184">
         <v>2017</v>
@@ -4742,10 +5329,13 @@
       <c r="G184">
         <v>30.83</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B185">
         <v>2018</v>
@@ -4765,10 +5355,13 @@
       <c r="G185">
         <v>48.97</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B186">
         <v>2019</v>
@@ -4788,10 +5381,13 @@
       <c r="G186">
         <v>45.51</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B187">
         <v>2020</v>
@@ -4811,10 +5407,13 @@
       <c r="G187">
         <v>38.840000000000003</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B188">
         <v>1990</v>
@@ -4834,10 +5433,13 @@
       <c r="G188">
         <v>30.91</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B189">
         <v>1991</v>
@@ -4857,10 +5459,13 @@
       <c r="G189">
         <v>49.41</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B190">
         <v>1992</v>
@@ -4880,10 +5485,13 @@
       <c r="G190">
         <v>34.24</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B191">
         <v>1993</v>
@@ -4903,10 +5511,13 @@
       <c r="G191">
         <v>51.9</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B192">
         <v>1994</v>
@@ -4926,10 +5537,13 @@
       <c r="G192">
         <v>41.17</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B193">
         <v>1995</v>
@@ -4949,10 +5563,13 @@
       <c r="G193">
         <v>45.84</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B194">
         <v>1996</v>
@@ -4972,10 +5589,13 @@
       <c r="G194">
         <v>51.42</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B195">
         <v>1997</v>
@@ -4995,10 +5615,13 @@
       <c r="G195">
         <v>59.21</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B196">
         <v>1998</v>
@@ -5018,10 +5641,13 @@
       <c r="G196">
         <v>43.81</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B197">
         <v>1999</v>
@@ -5041,10 +5667,13 @@
       <c r="G197">
         <v>51.61</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B198">
         <v>2000</v>
@@ -5064,10 +5693,13 @@
       <c r="G198">
         <v>40.229999999999997</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B199">
         <v>2001</v>
@@ -5087,10 +5719,13 @@
       <c r="G199">
         <v>47.77</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B200">
         <v>2002</v>
@@ -5110,10 +5745,13 @@
       <c r="G200">
         <v>55.49</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B201">
         <v>2003</v>
@@ -5133,10 +5771,13 @@
       <c r="G201">
         <v>30.25</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B202">
         <v>2004</v>
@@ -5156,10 +5797,13 @@
       <c r="G202">
         <v>30.13</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B203">
         <v>2005</v>
@@ -5179,10 +5823,13 @@
       <c r="G203">
         <v>44.01</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B204">
         <v>2006</v>
@@ -5202,10 +5849,13 @@
       <c r="G204">
         <v>50.2</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B205">
         <v>2007</v>
@@ -5225,10 +5875,13 @@
       <c r="G205">
         <v>50.36</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B206">
         <v>2008</v>
@@ -5248,10 +5901,13 @@
       <c r="G206">
         <v>45.88</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B207">
         <v>2009</v>
@@ -5271,10 +5927,13 @@
       <c r="G207">
         <v>54.47</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B208">
         <v>2010</v>
@@ -5294,10 +5953,13 @@
       <c r="G208">
         <v>41.82</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B209">
         <v>2011</v>
@@ -5317,10 +5979,13 @@
       <c r="G209">
         <v>50.31</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B210">
         <v>2012</v>
@@ -5340,10 +6005,13 @@
       <c r="G210">
         <v>51.86</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B211">
         <v>2013</v>
@@ -5363,10 +6031,13 @@
       <c r="G211">
         <v>59.81</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B212">
         <v>2014</v>
@@ -5386,10 +6057,13 @@
       <c r="G212">
         <v>41.82</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B213">
         <v>2015</v>
@@ -5409,10 +6083,13 @@
       <c r="G213">
         <v>56.95</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B214">
         <v>2016</v>
@@ -5432,10 +6109,13 @@
       <c r="G214">
         <v>49.45</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B215">
         <v>2017</v>
@@ -5455,10 +6135,13 @@
       <c r="G215">
         <v>39.93</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B216">
         <v>2018</v>
@@ -5478,10 +6161,13 @@
       <c r="G216">
         <v>45.54</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B217">
         <v>2019</v>
@@ -5501,10 +6187,13 @@
       <c r="G217">
         <v>51.12</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B218">
         <v>2020</v>
@@ -5524,10 +6213,13 @@
       <c r="G218">
         <v>35.950000000000003</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B219">
         <v>1990</v>
@@ -5547,10 +6239,13 @@
       <c r="G219">
         <v>38.119999999999997</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B220">
         <v>1991</v>
@@ -5570,10 +6265,13 @@
       <c r="G220">
         <v>39.200000000000003</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B221">
         <v>1992</v>
@@ -5593,10 +6291,13 @@
       <c r="G221">
         <v>30.74</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B222">
         <v>1993</v>
@@ -5616,10 +6317,13 @@
       <c r="G222">
         <v>31.61</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B223">
         <v>1994</v>
@@ -5639,10 +6343,13 @@
       <c r="G223">
         <v>36.700000000000003</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B224">
         <v>1995</v>
@@ -5662,10 +6369,13 @@
       <c r="G224">
         <v>50.69</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B225">
         <v>1996</v>
@@ -5685,10 +6395,13 @@
       <c r="G225">
         <v>44.14</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B226">
         <v>1997</v>
@@ -5708,10 +6421,13 @@
       <c r="G226">
         <v>43.3</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B227">
         <v>1998</v>
@@ -5731,10 +6447,13 @@
       <c r="G227">
         <v>37.61</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B228">
         <v>1999</v>
@@ -5754,10 +6473,13 @@
       <c r="G228">
         <v>57.2</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B229">
         <v>2000</v>
@@ -5777,10 +6499,13 @@
       <c r="G229">
         <v>37.93</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B230">
         <v>2001</v>
@@ -5800,10 +6525,13 @@
       <c r="G230">
         <v>50.38</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B231">
         <v>2002</v>
@@ -5823,10 +6551,13 @@
       <c r="G231">
         <v>57.46</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B232">
         <v>2003</v>
@@ -5846,10 +6577,13 @@
       <c r="G232">
         <v>35.65</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B233">
         <v>2004</v>
@@ -5869,10 +6603,13 @@
       <c r="G233">
         <v>49.45</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B234">
         <v>2005</v>
@@ -5892,10 +6629,13 @@
       <c r="G234">
         <v>55.29</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B235">
         <v>2006</v>
@@ -5915,10 +6655,13 @@
       <c r="G235">
         <v>56.09</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B236">
         <v>2007</v>
@@ -5938,10 +6681,13 @@
       <c r="G236">
         <v>52.22</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B237">
         <v>2008</v>
@@ -5961,10 +6707,13 @@
       <c r="G237">
         <v>58.01</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B238">
         <v>2009</v>
@@ -5984,10 +6733,13 @@
       <c r="G238">
         <v>44.45</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B239">
         <v>2010</v>
@@ -6007,10 +6759,13 @@
       <c r="G239">
         <v>59.27</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B240">
         <v>2011</v>
@@ -6030,10 +6785,13 @@
       <c r="G240">
         <v>52.14</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B241">
         <v>2012</v>
@@ -6053,10 +6811,13 @@
       <c r="G241">
         <v>50.04</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B242">
         <v>2013</v>
@@ -6076,10 +6837,13 @@
       <c r="G242">
         <v>34.99</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B243">
         <v>2014</v>
@@ -6099,10 +6863,13 @@
       <c r="G243">
         <v>52.95</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B244">
         <v>2015</v>
@@ -6122,10 +6889,13 @@
       <c r="G244">
         <v>48.85</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B245">
         <v>2016</v>
@@ -6145,10 +6915,13 @@
       <c r="G245">
         <v>38.94</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B246">
         <v>2017</v>
@@ -6168,10 +6941,13 @@
       <c r="G246">
         <v>52.69</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B247">
         <v>2018</v>
@@ -6191,10 +6967,13 @@
       <c r="G247">
         <v>34.93</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B248">
         <v>2019</v>
@@ -6214,10 +6993,13 @@
       <c r="G248">
         <v>32.9</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B249">
         <v>2020</v>
@@ -6237,10 +7019,13 @@
       <c r="G249">
         <v>35.409999999999997</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B250">
         <v>1990</v>
@@ -6260,10 +7045,13 @@
       <c r="G250">
         <v>30.05</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B251">
         <v>1991</v>
@@ -6283,10 +7071,13 @@
       <c r="G251">
         <v>48.04</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B252">
         <v>1992</v>
@@ -6306,10 +7097,13 @@
       <c r="G252">
         <v>42</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B253">
         <v>1993</v>
@@ -6329,10 +7123,13 @@
       <c r="G253">
         <v>43.91</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B254">
         <v>1994</v>
@@ -6352,10 +7149,13 @@
       <c r="G254">
         <v>50.82</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B255">
         <v>1995</v>
@@ -6375,10 +7175,13 @@
       <c r="G255">
         <v>52.41</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B256">
         <v>1996</v>
@@ -6398,10 +7201,13 @@
       <c r="G256">
         <v>30.25</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B257">
         <v>1997</v>
@@ -6421,10 +7227,13 @@
       <c r="G257">
         <v>46.92</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B258">
         <v>1998</v>
@@ -6444,10 +7253,13 @@
       <c r="G258">
         <v>31.79</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B259">
         <v>1999</v>
@@ -6467,10 +7279,13 @@
       <c r="G259">
         <v>36.369999999999997</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B260">
         <v>2000</v>
@@ -6490,10 +7305,13 @@
       <c r="G260">
         <v>51.84</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B261">
         <v>2001</v>
@@ -6513,10 +7331,13 @@
       <c r="G261">
         <v>39.81</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B262">
         <v>2002</v>
@@ -6536,10 +7357,13 @@
       <c r="G262">
         <v>37.24</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B263">
         <v>2003</v>
@@ -6559,10 +7383,13 @@
       <c r="G263">
         <v>46.24</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B264">
         <v>2004</v>
@@ -6582,10 +7409,13 @@
       <c r="G264">
         <v>33.54</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B265">
         <v>2005</v>
@@ -6605,10 +7435,13 @@
       <c r="G265">
         <v>58.35</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B266">
         <v>2006</v>
@@ -6628,10 +7461,13 @@
       <c r="G266">
         <v>59.18</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B267">
         <v>2007</v>
@@ -6651,10 +7487,13 @@
       <c r="G267">
         <v>48.54</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B268">
         <v>2008</v>
@@ -6674,10 +7513,13 @@
       <c r="G268">
         <v>48.06</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B269">
         <v>2009</v>
@@ -6697,10 +7539,13 @@
       <c r="G269">
         <v>42.43</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B270">
         <v>2010</v>
@@ -6720,10 +7565,13 @@
       <c r="G270">
         <v>37.700000000000003</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B271">
         <v>2011</v>
@@ -6743,10 +7591,13 @@
       <c r="G271">
         <v>42.79</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B272">
         <v>2012</v>
@@ -6766,10 +7617,13 @@
       <c r="G272">
         <v>31.48</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B273">
         <v>2013</v>
@@ -6789,10 +7643,13 @@
       <c r="G273">
         <v>37.270000000000003</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B274">
         <v>2014</v>
@@ -6812,10 +7669,13 @@
       <c r="G274">
         <v>32.700000000000003</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B275">
         <v>2015</v>
@@ -6835,10 +7695,13 @@
       <c r="G275">
         <v>37.11</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B276">
         <v>2016</v>
@@ -6858,10 +7721,13 @@
       <c r="G276">
         <v>53.7</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B277">
         <v>2017</v>
@@ -6881,10 +7747,13 @@
       <c r="G277">
         <v>44.4</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B278">
         <v>2018</v>
@@ -6904,10 +7773,13 @@
       <c r="G278">
         <v>58.41</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B279">
         <v>2019</v>
@@ -6927,10 +7799,13 @@
       <c r="G279">
         <v>34.92</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B280">
         <v>2020</v>
@@ -6950,10 +7825,13 @@
       <c r="G280">
         <v>50.7</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B281">
         <v>1990</v>
@@ -6973,10 +7851,13 @@
       <c r="G281">
         <v>35.409999999999997</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B282">
         <v>1991</v>
@@ -6996,10 +7877,13 @@
       <c r="G282">
         <v>33.79</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B283">
         <v>1992</v>
@@ -7019,10 +7903,13 @@
       <c r="G283">
         <v>51.57</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B284">
         <v>1993</v>
@@ -7042,10 +7929,13 @@
       <c r="G284">
         <v>41.65</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B285">
         <v>1994</v>
@@ -7065,10 +7955,13 @@
       <c r="G285">
         <v>45.84</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B286">
         <v>1995</v>
@@ -7088,10 +7981,13 @@
       <c r="G286">
         <v>46.02</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B287">
         <v>1996</v>
@@ -7111,10 +8007,13 @@
       <c r="G287">
         <v>45.19</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B288">
         <v>1997</v>
@@ -7134,10 +8033,13 @@
       <c r="G288">
         <v>49.29</v>
       </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B289">
         <v>1998</v>
@@ -7157,10 +8059,13 @@
       <c r="G289">
         <v>37.520000000000003</v>
       </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B290">
         <v>1999</v>
@@ -7180,10 +8085,13 @@
       <c r="G290">
         <v>43.53</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B291">
         <v>2000</v>
@@ -7203,10 +8111,13 @@
       <c r="G291">
         <v>49.77</v>
       </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B292">
         <v>2001</v>
@@ -7226,10 +8137,13 @@
       <c r="G292">
         <v>50.94</v>
       </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B293">
         <v>2002</v>
@@ -7249,10 +8163,13 @@
       <c r="G293">
         <v>34.89</v>
       </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B294">
         <v>2003</v>
@@ -7272,10 +8189,13 @@
       <c r="G294">
         <v>35.020000000000003</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B295">
         <v>2004</v>
@@ -7295,10 +8215,13 @@
       <c r="G295">
         <v>53.96</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B296">
         <v>2005</v>
@@ -7318,10 +8241,13 @@
       <c r="G296">
         <v>47.39</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B297">
         <v>2006</v>
@@ -7341,10 +8267,13 @@
       <c r="G297">
         <v>47.15</v>
       </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B298">
         <v>2007</v>
@@ -7364,10 +8293,13 @@
       <c r="G298">
         <v>45.33</v>
       </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B299">
         <v>2008</v>
@@ -7387,10 +8319,13 @@
       <c r="G299">
         <v>39.97</v>
       </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B300">
         <v>2009</v>
@@ -7410,10 +8345,13 @@
       <c r="G300">
         <v>32.119999999999997</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B301">
         <v>2010</v>
@@ -7433,10 +8371,13 @@
       <c r="G301">
         <v>37.729999999999997</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B302">
         <v>2011</v>
@@ -7456,10 +8397,13 @@
       <c r="G302">
         <v>34.26</v>
       </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B303">
         <v>2012</v>
@@ -7479,10 +8423,13 @@
       <c r="G303">
         <v>57.89</v>
       </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B304">
         <v>2013</v>
@@ -7502,10 +8449,13 @@
       <c r="G304">
         <v>45.54</v>
       </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B305">
         <v>2014</v>
@@ -7525,10 +8475,13 @@
       <c r="G305">
         <v>38.64</v>
       </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B306">
         <v>2015</v>
@@ -7548,10 +8501,13 @@
       <c r="G306">
         <v>33.31</v>
       </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B307">
         <v>2016</v>
@@ -7571,10 +8527,13 @@
       <c r="G307">
         <v>34.590000000000003</v>
       </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B308">
         <v>2017</v>
@@ -7594,10 +8553,13 @@
       <c r="G308">
         <v>47.1</v>
       </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B309">
         <v>2018</v>
@@ -7617,10 +8579,13 @@
       <c r="G309">
         <v>33.57</v>
       </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B310">
         <v>2019</v>
@@ -7640,10 +8605,13 @@
       <c r="G310">
         <v>46.25</v>
       </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B311">
         <v>2020</v>
@@ -7663,10 +8631,13 @@
       <c r="G311">
         <v>53.35</v>
       </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B312">
         <v>1990</v>
@@ -7686,10 +8657,13 @@
       <c r="G312">
         <v>41.51</v>
       </c>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B313">
         <v>1991</v>
@@ -7709,10 +8683,13 @@
       <c r="G313">
         <v>59.73</v>
       </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B314">
         <v>1992</v>
@@ -7732,10 +8709,13 @@
       <c r="G314">
         <v>45.78</v>
       </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B315">
         <v>1993</v>
@@ -7755,10 +8735,13 @@
       <c r="G315">
         <v>46.66</v>
       </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B316">
         <v>1994</v>
@@ -7778,10 +8761,13 @@
       <c r="G316">
         <v>51.8</v>
       </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B317">
         <v>1995</v>
@@ -7801,10 +8787,13 @@
       <c r="G317">
         <v>53.38</v>
       </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B318">
         <v>1996</v>
@@ -7824,10 +8813,13 @@
       <c r="G318">
         <v>59.44</v>
       </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B319">
         <v>1997</v>
@@ -7847,10 +8839,13 @@
       <c r="G319">
         <v>44.67</v>
       </c>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B320">
         <v>1998</v>
@@ -7870,10 +8865,13 @@
       <c r="G320">
         <v>55.46</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B321">
         <v>1999</v>
@@ -7893,10 +8891,13 @@
       <c r="G321">
         <v>58.46</v>
       </c>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B322">
         <v>2000</v>
@@ -7916,10 +8917,13 @@
       <c r="G322">
         <v>59.63</v>
       </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B323">
         <v>2001</v>
@@ -7939,10 +8943,13 @@
       <c r="G323">
         <v>33.08</v>
       </c>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B324">
         <v>2002</v>
@@ -7962,10 +8969,13 @@
       <c r="G324">
         <v>34.909999999999997</v>
       </c>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B325">
         <v>2003</v>
@@ -7985,10 +8995,13 @@
       <c r="G325">
         <v>39.08</v>
       </c>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B326">
         <v>2004</v>
@@ -8008,10 +9021,13 @@
       <c r="G326">
         <v>34.82</v>
       </c>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B327">
         <v>2005</v>
@@ -8031,10 +9047,13 @@
       <c r="G327">
         <v>33.17</v>
       </c>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B328">
         <v>2006</v>
@@ -8054,10 +9073,13 @@
       <c r="G328">
         <v>48.1</v>
       </c>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B329">
         <v>2007</v>
@@ -8077,10 +9099,13 @@
       <c r="G329">
         <v>31.46</v>
       </c>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B330">
         <v>2008</v>
@@ -8100,10 +9125,13 @@
       <c r="G330">
         <v>52.18</v>
       </c>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B331">
         <v>2009</v>
@@ -8123,10 +9151,13 @@
       <c r="G331">
         <v>34.83</v>
       </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B332">
         <v>2010</v>
@@ -8146,10 +9177,13 @@
       <c r="G332">
         <v>58.18</v>
       </c>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B333">
         <v>2011</v>
@@ -8169,10 +9203,13 @@
       <c r="G333">
         <v>55.18</v>
       </c>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -8192,10 +9229,13 @@
       <c r="G334">
         <v>54.17</v>
       </c>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B335">
         <v>2013</v>
@@ -8215,10 +9255,13 @@
       <c r="G335">
         <v>51.36</v>
       </c>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B336">
         <v>2014</v>
@@ -8238,10 +9281,13 @@
       <c r="G336">
         <v>47.46</v>
       </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B337">
         <v>2015</v>
@@ -8261,10 +9307,13 @@
       <c r="G337">
         <v>30.34</v>
       </c>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B338">
         <v>2016</v>
@@ -8284,10 +9333,13 @@
       <c r="G338">
         <v>54.21</v>
       </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B339">
         <v>2017</v>
@@ -8307,10 +9359,13 @@
       <c r="G339">
         <v>51.1</v>
       </c>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B340">
         <v>2018</v>
@@ -8330,10 +9385,13 @@
       <c r="G340">
         <v>52.54</v>
       </c>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B341">
         <v>2019</v>
@@ -8353,10 +9411,13 @@
       <c r="G341">
         <v>47.21</v>
       </c>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B342">
         <v>2020</v>
@@ -8376,10 +9437,13 @@
       <c r="G342">
         <v>31.25</v>
       </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B343">
         <v>1990</v>
@@ -8399,10 +9463,13 @@
       <c r="G343">
         <v>50.07</v>
       </c>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B344">
         <v>1991</v>
@@ -8422,10 +9489,13 @@
       <c r="G344">
         <v>57.86</v>
       </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B345">
         <v>1992</v>
@@ -8445,10 +9515,13 @@
       <c r="G345">
         <v>47.64</v>
       </c>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B346">
         <v>1993</v>
@@ -8468,10 +9541,13 @@
       <c r="G346">
         <v>35.97</v>
       </c>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B347">
         <v>1994</v>
@@ -8491,10 +9567,13 @@
       <c r="G347">
         <v>54.02</v>
       </c>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B348">
         <v>1995</v>
@@ -8514,10 +9593,13 @@
       <c r="G348">
         <v>51.88</v>
       </c>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B349">
         <v>1996</v>
@@ -8537,10 +9619,13 @@
       <c r="G349">
         <v>39.950000000000003</v>
       </c>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B350">
         <v>1997</v>
@@ -8560,10 +9645,13 @@
       <c r="G350">
         <v>35.75</v>
       </c>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B351">
         <v>1998</v>
@@ -8583,10 +9671,13 @@
       <c r="G351">
         <v>44.77</v>
       </c>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B352">
         <v>1999</v>
@@ -8606,10 +9697,13 @@
       <c r="G352">
         <v>56.52</v>
       </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B353">
         <v>2000</v>
@@ -8629,10 +9723,13 @@
       <c r="G353">
         <v>31.13</v>
       </c>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B354">
         <v>2001</v>
@@ -8652,10 +9749,13 @@
       <c r="G354">
         <v>54.05</v>
       </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B355">
         <v>2002</v>
@@ -8675,10 +9775,13 @@
       <c r="G355">
         <v>46.81</v>
       </c>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B356">
         <v>2003</v>
@@ -8698,10 +9801,13 @@
       <c r="G356">
         <v>57.63</v>
       </c>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B357">
         <v>2004</v>
@@ -8721,10 +9827,13 @@
       <c r="G357">
         <v>45.98</v>
       </c>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B358">
         <v>2005</v>
@@ -8744,10 +9853,13 @@
       <c r="G358">
         <v>53.41</v>
       </c>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B359">
         <v>2006</v>
@@ -8767,10 +9879,13 @@
       <c r="G359">
         <v>31.81</v>
       </c>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B360">
         <v>2007</v>
@@ -8790,10 +9905,13 @@
       <c r="G360">
         <v>55.14</v>
       </c>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B361">
         <v>2008</v>
@@ -8813,10 +9931,13 @@
       <c r="G361">
         <v>59.57</v>
       </c>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B362">
         <v>2009</v>
@@ -8836,10 +9957,13 @@
       <c r="G362">
         <v>47.02</v>
       </c>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B363">
         <v>2010</v>
@@ -8859,10 +9983,13 @@
       <c r="G363">
         <v>46.55</v>
       </c>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B364">
         <v>2011</v>
@@ -8882,10 +10009,13 @@
       <c r="G364">
         <v>49.38</v>
       </c>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B365">
         <v>2012</v>
@@ -8905,10 +10035,13 @@
       <c r="G365">
         <v>48.01</v>
       </c>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B366">
         <v>2013</v>
@@ -8928,10 +10061,13 @@
       <c r="G366">
         <v>32.590000000000003</v>
       </c>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B367">
         <v>2014</v>
@@ -8951,10 +10087,13 @@
       <c r="G367">
         <v>32.979999999999997</v>
       </c>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B368">
         <v>2015</v>
@@ -8974,10 +10113,13 @@
       <c r="G368">
         <v>30.19</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B369">
         <v>2016</v>
@@ -8997,10 +10139,13 @@
       <c r="G369">
         <v>50.75</v>
       </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B370">
         <v>2017</v>
@@ -9020,10 +10165,13 @@
       <c r="G370">
         <v>45.46</v>
       </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B371">
         <v>2018</v>
@@ -9043,10 +10191,13 @@
       <c r="G371">
         <v>36.700000000000003</v>
       </c>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B372">
         <v>2019</v>
@@ -9066,10 +10217,13 @@
       <c r="G372">
         <v>48.9</v>
       </c>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B373">
         <v>2020</v>
@@ -9089,10 +10243,13 @@
       <c r="G373">
         <v>58.42</v>
       </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B374">
         <v>1990</v>
@@ -9112,10 +10269,13 @@
       <c r="G374">
         <v>47.38</v>
       </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B375">
         <v>1991</v>
@@ -9135,10 +10295,13 @@
       <c r="G375">
         <v>35.69</v>
       </c>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B376">
         <v>1992</v>
@@ -9158,10 +10321,13 @@
       <c r="G376">
         <v>51.15</v>
       </c>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B377">
         <v>1993</v>
@@ -9181,10 +10347,13 @@
       <c r="G377">
         <v>59.49</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B378">
         <v>1994</v>
@@ -9204,10 +10373,13 @@
       <c r="G378">
         <v>52.55</v>
       </c>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B379">
         <v>1995</v>
@@ -9227,10 +10399,13 @@
       <c r="G379">
         <v>53.68</v>
       </c>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B380">
         <v>1996</v>
@@ -9250,10 +10425,13 @@
       <c r="G380">
         <v>54.22</v>
       </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B381">
         <v>1997</v>
@@ -9273,10 +10451,13 @@
       <c r="G381">
         <v>34.32</v>
       </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B382">
         <v>1998</v>
@@ -9296,10 +10477,13 @@
       <c r="G382">
         <v>59.02</v>
       </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B383">
         <v>1999</v>
@@ -9319,10 +10503,13 @@
       <c r="G383">
         <v>54.48</v>
       </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B384">
         <v>2000</v>
@@ -9342,10 +10529,13 @@
       <c r="G384">
         <v>55.85</v>
       </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B385">
         <v>2001</v>
@@ -9365,10 +10555,13 @@
       <c r="G385">
         <v>36.119999999999997</v>
       </c>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B386">
         <v>2002</v>
@@ -9388,10 +10581,13 @@
       <c r="G386">
         <v>58.67</v>
       </c>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B387">
         <v>2003</v>
@@ -9411,10 +10607,13 @@
       <c r="G387">
         <v>55</v>
       </c>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B388">
         <v>2004</v>
@@ -9434,10 +10633,13 @@
       <c r="G388">
         <v>51.5</v>
       </c>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B389">
         <v>2005</v>
@@ -9457,10 +10659,13 @@
       <c r="G389">
         <v>39.4</v>
       </c>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B390">
         <v>2006</v>
@@ -9480,10 +10685,13 @@
       <c r="G390">
         <v>35.69</v>
       </c>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B391">
         <v>2007</v>
@@ -9503,10 +10711,13 @@
       <c r="G391">
         <v>38.159999999999997</v>
       </c>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B392">
         <v>2008</v>
@@ -9526,10 +10737,13 @@
       <c r="G392">
         <v>49.98</v>
       </c>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B393">
         <v>2009</v>
@@ -9549,10 +10763,13 @@
       <c r="G393">
         <v>42.27</v>
       </c>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B394">
         <v>2010</v>
@@ -9572,10 +10789,13 @@
       <c r="G394">
         <v>44.41</v>
       </c>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B395">
         <v>2011</v>
@@ -9595,10 +10815,13 @@
       <c r="G395">
         <v>36.47</v>
       </c>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B396">
         <v>2012</v>
@@ -9618,10 +10841,13 @@
       <c r="G396">
         <v>47.36</v>
       </c>
-    </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B397">
         <v>2013</v>
@@ -9641,10 +10867,13 @@
       <c r="G397">
         <v>45.83</v>
       </c>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B398">
         <v>2014</v>
@@ -9664,10 +10893,13 @@
       <c r="G398">
         <v>47.37</v>
       </c>
-    </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B399">
         <v>2015</v>
@@ -9687,10 +10919,13 @@
       <c r="G399">
         <v>37.340000000000003</v>
       </c>
-    </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B400">
         <v>2016</v>
@@ -9710,10 +10945,13 @@
       <c r="G400">
         <v>54.37</v>
       </c>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B401">
         <v>2017</v>
@@ -9733,10 +10971,13 @@
       <c r="G401">
         <v>51.67</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B402">
         <v>2018</v>
@@ -9756,10 +10997,13 @@
       <c r="G402">
         <v>58.59</v>
       </c>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B403">
         <v>2019</v>
@@ -9779,10 +11023,13 @@
       <c r="G403">
         <v>53.73</v>
       </c>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B404">
         <v>2020</v>
@@ -9802,10 +11049,13 @@
       <c r="G404">
         <v>30.2</v>
       </c>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B405">
         <v>1990</v>
@@ -9825,10 +11075,13 @@
       <c r="G405">
         <v>59.79</v>
       </c>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B406">
         <v>1991</v>
@@ -9848,10 +11101,13 @@
       <c r="G406">
         <v>47.66</v>
       </c>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B407">
         <v>1992</v>
@@ -9871,10 +11127,13 @@
       <c r="G407">
         <v>35.51</v>
       </c>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B408">
         <v>1993</v>
@@ -9894,10 +11153,13 @@
       <c r="G408">
         <v>41.73</v>
       </c>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B409">
         <v>1994</v>
@@ -9917,10 +11179,13 @@
       <c r="G409">
         <v>58.13</v>
       </c>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H409">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B410">
         <v>1995</v>
@@ -9940,10 +11205,13 @@
       <c r="G410">
         <v>43.96</v>
       </c>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B411">
         <v>1996</v>
@@ -9963,10 +11231,13 @@
       <c r="G411">
         <v>54.95</v>
       </c>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B412">
         <v>1997</v>
@@ -9986,10 +11257,13 @@
       <c r="G412">
         <v>51.63</v>
       </c>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B413">
         <v>1998</v>
@@ -10009,10 +11283,13 @@
       <c r="G413">
         <v>56.59</v>
       </c>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B414">
         <v>1999</v>
@@ -10032,10 +11309,13 @@
       <c r="G414">
         <v>31.61</v>
       </c>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B415">
         <v>2000</v>
@@ -10055,10 +11335,13 @@
       <c r="G415">
         <v>35.590000000000003</v>
       </c>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B416">
         <v>2001</v>
@@ -10078,10 +11361,13 @@
       <c r="G416">
         <v>55.46</v>
       </c>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H416">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B417">
         <v>2002</v>
@@ -10101,10 +11387,13 @@
       <c r="G417">
         <v>50.29</v>
       </c>
-    </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B418">
         <v>2003</v>
@@ -10124,10 +11413,13 @@
       <c r="G418">
         <v>35.6</v>
       </c>
-    </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B419">
         <v>2004</v>
@@ -10147,10 +11439,13 @@
       <c r="G419">
         <v>58.84</v>
       </c>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B420">
         <v>2005</v>
@@ -10170,10 +11465,13 @@
       <c r="G420">
         <v>31.51</v>
       </c>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B421">
         <v>2006</v>
@@ -10193,10 +11491,13 @@
       <c r="G421">
         <v>48.81</v>
       </c>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B422">
         <v>2007</v>
@@ -10216,10 +11517,13 @@
       <c r="G422">
         <v>45.52</v>
       </c>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B423">
         <v>2008</v>
@@ -10239,10 +11543,13 @@
       <c r="G423">
         <v>39.770000000000003</v>
       </c>
-    </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B424">
         <v>2009</v>
@@ -10262,10 +11569,13 @@
       <c r="G424">
         <v>36.090000000000003</v>
       </c>
-    </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B425">
         <v>2010</v>
@@ -10285,10 +11595,13 @@
       <c r="G425">
         <v>47</v>
       </c>
-    </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B426">
         <v>2011</v>
@@ -10308,10 +11621,13 @@
       <c r="G426">
         <v>40.72</v>
       </c>
-    </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B427">
         <v>2012</v>
@@ -10331,10 +11647,13 @@
       <c r="G427">
         <v>39.909999999999997</v>
       </c>
-    </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B428">
         <v>2013</v>
@@ -10354,10 +11673,13 @@
       <c r="G428">
         <v>56.86</v>
       </c>
-    </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B429">
         <v>2014</v>
@@ -10377,10 +11699,13 @@
       <c r="G429">
         <v>51.31</v>
       </c>
-    </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B430">
         <v>2015</v>
@@ -10400,10 +11725,13 @@
       <c r="G430">
         <v>45.84</v>
       </c>
-    </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B431">
         <v>2016</v>
@@ -10423,10 +11751,13 @@
       <c r="G431">
         <v>41.89</v>
       </c>
-    </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B432">
         <v>2017</v>
@@ -10446,10 +11777,13 @@
       <c r="G432">
         <v>30.46</v>
       </c>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B433">
         <v>2018</v>
@@ -10469,10 +11803,13 @@
       <c r="G433">
         <v>51.17</v>
       </c>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B434">
         <v>2019</v>
@@ -10492,10 +11829,13 @@
       <c r="G434">
         <v>30.57</v>
       </c>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B435">
         <v>2020</v>
@@ -10515,10 +11855,13 @@
       <c r="G435">
         <v>55.88</v>
       </c>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B436">
         <v>1990</v>
@@ -10538,10 +11881,13 @@
       <c r="G436">
         <v>43.67</v>
       </c>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B437">
         <v>1991</v>
@@ -10561,10 +11907,13 @@
       <c r="G437">
         <v>52.1</v>
       </c>
-    </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B438">
         <v>1992</v>
@@ -10584,10 +11933,13 @@
       <c r="G438">
         <v>32.01</v>
       </c>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B439">
         <v>1993</v>
@@ -10607,10 +11959,13 @@
       <c r="G439">
         <v>59.44</v>
       </c>
-    </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B440">
         <v>1994</v>
@@ -10630,10 +11985,13 @@
       <c r="G440">
         <v>40.26</v>
       </c>
-    </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B441">
         <v>1995</v>
@@ -10653,10 +12011,13 @@
       <c r="G441">
         <v>56.64</v>
       </c>
-    </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B442">
         <v>1996</v>
@@ -10676,10 +12037,13 @@
       <c r="G442">
         <v>55.94</v>
       </c>
-    </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B443">
         <v>1997</v>
@@ -10699,10 +12063,13 @@
       <c r="G443">
         <v>54.96</v>
       </c>
-    </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B444">
         <v>1998</v>
@@ -10722,10 +12089,13 @@
       <c r="G444">
         <v>57.16</v>
       </c>
-    </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B445">
         <v>1999</v>
@@ -10745,10 +12115,13 @@
       <c r="G445">
         <v>54.26</v>
       </c>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B446">
         <v>2000</v>
@@ -10768,10 +12141,13 @@
       <c r="G446">
         <v>49.41</v>
       </c>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B447">
         <v>2001</v>
@@ -10791,10 +12167,13 @@
       <c r="G447">
         <v>41.52</v>
       </c>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B448">
         <v>2002</v>
@@ -10814,10 +12193,13 @@
       <c r="G448">
         <v>43.8</v>
       </c>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B449">
         <v>2003</v>
@@ -10837,10 +12219,13 @@
       <c r="G449">
         <v>46.58</v>
       </c>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B450">
         <v>2004</v>
@@ -10860,10 +12245,13 @@
       <c r="G450">
         <v>32.51</v>
       </c>
-    </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B451">
         <v>2005</v>
@@ -10883,10 +12271,13 @@
       <c r="G451">
         <v>38.6</v>
       </c>
-    </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B452">
         <v>2006</v>
@@ -10906,10 +12297,13 @@
       <c r="G452">
         <v>41.9</v>
       </c>
-    </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B453">
         <v>2007</v>
@@ -10929,10 +12323,13 @@
       <c r="G453">
         <v>51.04</v>
       </c>
-    </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B454">
         <v>2008</v>
@@ -10952,10 +12349,13 @@
       <c r="G454">
         <v>46.19</v>
       </c>
-    </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B455">
         <v>2009</v>
@@ -10975,10 +12375,13 @@
       <c r="G455">
         <v>32.25</v>
       </c>
-    </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H455">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B456">
         <v>2010</v>
@@ -10998,10 +12401,13 @@
       <c r="G456">
         <v>51.26</v>
       </c>
-    </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B457">
         <v>2011</v>
@@ -11021,10 +12427,13 @@
       <c r="G457">
         <v>46.24</v>
       </c>
-    </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B458">
         <v>2012</v>
@@ -11044,10 +12453,13 @@
       <c r="G458">
         <v>58.33</v>
       </c>
-    </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B459">
         <v>2013</v>
@@ -11067,10 +12479,13 @@
       <c r="G459">
         <v>32.72</v>
       </c>
-    </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B460">
         <v>2014</v>
@@ -11090,10 +12505,13 @@
       <c r="G460">
         <v>32.659999999999997</v>
       </c>
-    </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B461">
         <v>2015</v>
@@ -11113,10 +12531,13 @@
       <c r="G461">
         <v>34.93</v>
       </c>
-    </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B462">
         <v>2016</v>
@@ -11136,10 +12557,13 @@
       <c r="G462">
         <v>42.64</v>
       </c>
-    </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H462">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B463">
         <v>2017</v>
@@ -11159,10 +12583,13 @@
       <c r="G463">
         <v>34.54</v>
       </c>
-    </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H463">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B464">
         <v>2018</v>
@@ -11182,10 +12609,13 @@
       <c r="G464">
         <v>46.1</v>
       </c>
-    </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H464">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B465">
         <v>2019</v>
@@ -11205,10 +12635,13 @@
       <c r="G465">
         <v>43.16</v>
       </c>
-    </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B466">
         <v>2020</v>
@@ -11228,10 +12661,13 @@
       <c r="G466">
         <v>37.1</v>
       </c>
-    </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B467">
         <v>1990</v>
@@ -11251,10 +12687,13 @@
       <c r="G467">
         <v>59.26</v>
       </c>
-    </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H467">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B468">
         <v>1991</v>
@@ -11274,10 +12713,13 @@
       <c r="G468">
         <v>52.83</v>
       </c>
-    </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H468">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B469">
         <v>1992</v>
@@ -11297,10 +12739,13 @@
       <c r="G469">
         <v>43.05</v>
       </c>
-    </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H469">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B470">
         <v>1993</v>
@@ -11320,10 +12765,13 @@
       <c r="G470">
         <v>59.53</v>
       </c>
-    </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H470">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B471">
         <v>1994</v>
@@ -11343,10 +12791,13 @@
       <c r="G471">
         <v>50.27</v>
       </c>
-    </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B472">
         <v>1995</v>
@@ -11366,10 +12817,13 @@
       <c r="G472">
         <v>44.76</v>
       </c>
-    </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B473">
         <v>1996</v>
@@ -11389,10 +12843,13 @@
       <c r="G473">
         <v>56.96</v>
       </c>
-    </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H473">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B474">
         <v>1997</v>
@@ -11412,10 +12869,13 @@
       <c r="G474">
         <v>38.54</v>
       </c>
-    </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B475">
         <v>1998</v>
@@ -11435,10 +12895,13 @@
       <c r="G475">
         <v>53.14</v>
       </c>
-    </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H475">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B476">
         <v>1999</v>
@@ -11458,10 +12921,13 @@
       <c r="G476">
         <v>51.7</v>
       </c>
-    </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B477">
         <v>2000</v>
@@ -11481,10 +12947,13 @@
       <c r="G477">
         <v>39.96</v>
       </c>
-    </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B478">
         <v>2001</v>
@@ -11504,10 +12973,13 @@
       <c r="G478">
         <v>48.43</v>
       </c>
-    </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B479">
         <v>2002</v>
@@ -11527,10 +12999,13 @@
       <c r="G479">
         <v>33.79</v>
       </c>
-    </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B480">
         <v>2003</v>
@@ -11550,10 +13025,13 @@
       <c r="G480">
         <v>34.58</v>
       </c>
-    </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B481">
         <v>2004</v>
@@ -11573,10 +13051,13 @@
       <c r="G481">
         <v>44.32</v>
       </c>
-    </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H481">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B482">
         <v>2005</v>
@@ -11596,10 +13077,13 @@
       <c r="G482">
         <v>50.57</v>
       </c>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B483">
         <v>2006</v>
@@ -11619,10 +13103,13 @@
       <c r="G483">
         <v>54.58</v>
       </c>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B484">
         <v>2007</v>
@@ -11642,10 +13129,13 @@
       <c r="G484">
         <v>35.86</v>
       </c>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H484">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B485">
         <v>2008</v>
@@ -11665,10 +13155,13 @@
       <c r="G485">
         <v>56.87</v>
       </c>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B486">
         <v>2009</v>
@@ -11688,10 +13181,13 @@
       <c r="G486">
         <v>35.49</v>
       </c>
-    </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B487">
         <v>2010</v>
@@ -11711,10 +13207,13 @@
       <c r="G487">
         <v>48.9</v>
       </c>
-    </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B488">
         <v>2011</v>
@@ -11734,10 +13233,13 @@
       <c r="G488">
         <v>56.92</v>
       </c>
-    </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B489">
         <v>2012</v>
@@ -11757,10 +13259,13 @@
       <c r="G489">
         <v>59.02</v>
       </c>
-    </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H489">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B490">
         <v>2013</v>
@@ -11780,10 +13285,13 @@
       <c r="G490">
         <v>31.83</v>
       </c>
-    </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B491">
         <v>2014</v>
@@ -11803,10 +13311,13 @@
       <c r="G491">
         <v>36.86</v>
       </c>
-    </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B492">
         <v>2015</v>
@@ -11826,10 +13337,13 @@
       <c r="G492">
         <v>49.64</v>
       </c>
-    </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H492">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B493">
         <v>2016</v>
@@ -11849,10 +13363,13 @@
       <c r="G493">
         <v>46.94</v>
       </c>
-    </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H493">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B494">
         <v>2017</v>
@@ -11872,10 +13389,13 @@
       <c r="G494">
         <v>35.909999999999997</v>
       </c>
-    </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B495">
         <v>2018</v>
@@ -11895,10 +13415,13 @@
       <c r="G495">
         <v>44.93</v>
       </c>
-    </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B496">
         <v>2019</v>
@@ -11918,10 +13441,13 @@
       <c r="G496">
         <v>51.81</v>
       </c>
-    </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B497">
         <v>2020</v>
@@ -11941,10 +13467,13 @@
       <c r="G497">
         <v>41.3</v>
       </c>
-    </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B498">
         <v>1990</v>
@@ -11964,10 +13493,13 @@
       <c r="G498">
         <v>51.4</v>
       </c>
-    </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H498">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B499">
         <v>1991</v>
@@ -11987,10 +13519,13 @@
       <c r="G499">
         <v>56.37</v>
       </c>
-    </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B500">
         <v>1992</v>
@@ -12010,10 +13545,13 @@
       <c r="G500">
         <v>55.93</v>
       </c>
-    </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H500">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B501">
         <v>1993</v>
@@ -12033,10 +13571,13 @@
       <c r="G501">
         <v>53.39</v>
       </c>
-    </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B502">
         <v>1994</v>
@@ -12056,10 +13597,13 @@
       <c r="G502">
         <v>56.16</v>
       </c>
-    </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B503">
         <v>1995</v>
@@ -12079,10 +13623,13 @@
       <c r="G503">
         <v>50.62</v>
       </c>
-    </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H503">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B504">
         <v>1996</v>
@@ -12102,10 +13649,13 @@
       <c r="G504">
         <v>38.1</v>
       </c>
-    </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H504">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B505">
         <v>1997</v>
@@ -12125,10 +13675,13 @@
       <c r="G505">
         <v>50.41</v>
       </c>
-    </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H505">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B506">
         <v>1998</v>
@@ -12148,10 +13701,13 @@
       <c r="G506">
         <v>59</v>
       </c>
-    </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B507">
         <v>1999</v>
@@ -12171,10 +13727,13 @@
       <c r="G507">
         <v>57.24</v>
       </c>
-    </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H507">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B508">
         <v>2000</v>
@@ -12194,10 +13753,13 @@
       <c r="G508">
         <v>47.83</v>
       </c>
-    </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H508">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B509">
         <v>2001</v>
@@ -12217,10 +13779,13 @@
       <c r="G509">
         <v>49.52</v>
       </c>
-    </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B510">
         <v>2002</v>
@@ -12240,10 +13805,13 @@
       <c r="G510">
         <v>57.24</v>
       </c>
-    </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H510">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B511">
         <v>2003</v>
@@ -12263,10 +13831,13 @@
       <c r="G511">
         <v>54.07</v>
       </c>
-    </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B512">
         <v>2004</v>
@@ -12286,10 +13857,13 @@
       <c r="G512">
         <v>56.28</v>
       </c>
-    </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B513">
         <v>2005</v>
@@ -12309,10 +13883,13 @@
       <c r="G513">
         <v>50.74</v>
       </c>
-    </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H513">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B514">
         <v>2006</v>
@@ -12332,10 +13909,13 @@
       <c r="G514">
         <v>40.090000000000003</v>
       </c>
-    </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H514">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B515">
         <v>2007</v>
@@ -12355,10 +13935,13 @@
       <c r="G515">
         <v>34.68</v>
       </c>
-    </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H515">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B516">
         <v>2008</v>
@@ -12378,10 +13961,13 @@
       <c r="G516">
         <v>43.56</v>
       </c>
-    </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B517">
         <v>2009</v>
@@ -12401,10 +13987,13 @@
       <c r="G517">
         <v>58.09</v>
       </c>
-    </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B518">
         <v>2010</v>
@@ -12424,10 +14013,13 @@
       <c r="G518">
         <v>59.36</v>
       </c>
-    </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H518">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B519">
         <v>2011</v>
@@ -12447,10 +14039,13 @@
       <c r="G519">
         <v>32.5</v>
       </c>
-    </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B520">
         <v>2012</v>
@@ -12470,10 +14065,13 @@
       <c r="G520">
         <v>36.92</v>
       </c>
-    </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B521">
         <v>2013</v>
@@ -12493,10 +14091,13 @@
       <c r="G521">
         <v>45.4</v>
       </c>
-    </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H521">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B522">
         <v>2014</v>
@@ -12516,10 +14117,13 @@
       <c r="G522">
         <v>45.69</v>
       </c>
-    </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B523">
         <v>2015</v>
@@ -12539,10 +14143,13 @@
       <c r="G523">
         <v>55.82</v>
       </c>
-    </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B524">
         <v>2016</v>
@@ -12562,10 +14169,13 @@
       <c r="G524">
         <v>37.83</v>
       </c>
-    </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B525">
         <v>2017</v>
@@ -12585,10 +14195,13 @@
       <c r="G525">
         <v>44.96</v>
       </c>
-    </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B526">
         <v>2018</v>
@@ -12608,10 +14221,13 @@
       <c r="G526">
         <v>56.33</v>
       </c>
-    </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B527">
         <v>2019</v>
@@ -12631,10 +14247,13 @@
       <c r="G527">
         <v>44.88</v>
       </c>
-    </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B528">
         <v>2020</v>
@@ -12654,10 +14273,13 @@
       <c r="G528">
         <v>35.200000000000003</v>
       </c>
-    </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B529">
         <v>1990</v>
@@ -12677,10 +14299,13 @@
       <c r="G529">
         <v>57.19</v>
       </c>
-    </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B530">
         <v>1991</v>
@@ -12700,10 +14325,13 @@
       <c r="G530">
         <v>52.56</v>
       </c>
-    </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B531">
         <v>1992</v>
@@ -12723,10 +14351,13 @@
       <c r="G531">
         <v>36.35</v>
       </c>
-    </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B532">
         <v>1993</v>
@@ -12746,10 +14377,13 @@
       <c r="G532">
         <v>34.46</v>
       </c>
-    </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H532">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B533">
         <v>1994</v>
@@ -12769,10 +14403,13 @@
       <c r="G533">
         <v>47.77</v>
       </c>
-    </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B534">
         <v>1995</v>
@@ -12792,10 +14429,13 @@
       <c r="G534">
         <v>53.48</v>
       </c>
-    </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B535">
         <v>1996</v>
@@ -12815,10 +14455,13 @@
       <c r="G535">
         <v>45.17</v>
       </c>
-    </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B536">
         <v>1997</v>
@@ -12838,10 +14481,13 @@
       <c r="G536">
         <v>53.79</v>
       </c>
-    </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H536">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B537">
         <v>1998</v>
@@ -12861,10 +14507,13 @@
       <c r="G537">
         <v>36.86</v>
       </c>
-    </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H537">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B538">
         <v>1999</v>
@@ -12884,10 +14533,13 @@
       <c r="G538">
         <v>51.69</v>
       </c>
-    </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B539">
         <v>2000</v>
@@ -12907,10 +14559,13 @@
       <c r="G539">
         <v>51.12</v>
       </c>
-    </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H539">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B540">
         <v>2001</v>
@@ -12930,10 +14585,13 @@
       <c r="G540">
         <v>33.61</v>
       </c>
-    </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B541">
         <v>2002</v>
@@ -12953,10 +14611,13 @@
       <c r="G541">
         <v>57.97</v>
       </c>
-    </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H541">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B542">
         <v>2003</v>
@@ -12976,10 +14637,13 @@
       <c r="G542">
         <v>40.659999999999997</v>
       </c>
-    </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B543">
         <v>2004</v>
@@ -12999,10 +14663,13 @@
       <c r="G543">
         <v>40.72</v>
       </c>
-    </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H543">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B544">
         <v>2005</v>
@@ -13022,10 +14689,13 @@
       <c r="G544">
         <v>45.86</v>
       </c>
-    </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B545">
         <v>2006</v>
@@ -13045,10 +14715,13 @@
       <c r="G545">
         <v>59.69</v>
       </c>
-    </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H545">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B546">
         <v>2007</v>
@@ -13068,10 +14741,13 @@
       <c r="G546">
         <v>32.950000000000003</v>
       </c>
-    </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H546">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B547">
         <v>2008</v>
@@ -13091,10 +14767,13 @@
       <c r="G547">
         <v>39.58</v>
       </c>
-    </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B548">
         <v>2009</v>
@@ -13114,10 +14793,13 @@
       <c r="G548">
         <v>45.36</v>
       </c>
-    </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H548">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B549">
         <v>2010</v>
@@ -13137,10 +14819,13 @@
       <c r="G549">
         <v>34.44</v>
       </c>
-    </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B550">
         <v>2011</v>
@@ -13160,10 +14845,13 @@
       <c r="G550">
         <v>42.98</v>
       </c>
-    </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H550">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B551">
         <v>2012</v>
@@ -13183,10 +14871,13 @@
       <c r="G551">
         <v>44.21</v>
       </c>
-    </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B552">
         <v>2013</v>
@@ -13206,10 +14897,13 @@
       <c r="G552">
         <v>43.35</v>
       </c>
-    </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H552">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B553">
         <v>2014</v>
@@ -13229,10 +14923,13 @@
       <c r="G553">
         <v>36.64</v>
       </c>
-    </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B554">
         <v>2015</v>
@@ -13252,10 +14949,13 @@
       <c r="G554">
         <v>32.61</v>
       </c>
-    </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H554">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B555">
         <v>2016</v>
@@ -13275,10 +14975,13 @@
       <c r="G555">
         <v>57.61</v>
       </c>
-    </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B556">
         <v>2017</v>
@@ -13298,10 +15001,13 @@
       <c r="G556">
         <v>54.8</v>
       </c>
-    </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B557">
         <v>2018</v>
@@ -13321,10 +15027,13 @@
       <c r="G557">
         <v>58.3</v>
       </c>
-    </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H557">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B558">
         <v>2019</v>
@@ -13344,10 +15053,13 @@
       <c r="G558">
         <v>37.450000000000003</v>
       </c>
-    </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B559">
         <v>2020</v>
@@ -13367,9 +15079,11 @@
       <c r="G559">
         <v>31.75</v>
       </c>
+      <c r="H559">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13385,72 +15099,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
         <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>